--- a/AIVIA_Design/L1_KG3_Artifact_Layer_Registry_DRAFT.xlsx
+++ b/AIVIA_Design/L1_KG3_Artifact_Layer_Registry_DRAFT.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Classes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Rules_to_Checks" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Fixture_Families" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Lifecycle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1137,4 +1138,156 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Writer / trigger</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>per class: descriptions+nominations &lt;- generation pipeline (agent identity); dispositions &lt;- human surface (HUMAN ONLY); usage &lt;- ask surface; proposals &lt;- bridge; human-authored terms/responsibilities &lt;- human surface</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>spine complete (about resolves any lower-or-same layer; author -&gt; identity node; basis on machine versions; status in closed vocab); machine text gated; total gate failure -&gt; NO artifact + run-event accounting</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>LC3-C1 per class authored input -&gt; authored artifact · LC3-C2 gate failure -&gt; absence + counted · LC3-C3 disposition w/ agent author -&gt; refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SUPERSEDE</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>state-shaped only; same writers; humans via the human surface</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>new version + supersedes edge; machine append on human-owned renders PROPOSED, never current</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>LC3-S1 human edit -&gt; ownership flips (derived) · LC3-S2 machine append on human-owned -&gt; proposed · LC3-S3 events never supersede (no path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RETIRE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>NOBODY — the action does not exist in this layer; ending is done BY WRITING (revoking disposition, superseding version)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>LC3-R1 no retire path exists (structural)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>anyone</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>current/standing/ownership via lenses only</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>LC3-D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FORBIDDEN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>machine dispositions (LC3-F1) · pipeline current over human-owned (LC3-F2) · in-place edit (LC3-F3) · ANY deletion (LC3-F4 — absolute; PHI tension recorded as H6, SAFETY pass owes reconciliation) · empty shells (LC3-F5)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>